--- a/tests/fixtures/kb/past_answers/past_answer_2024.xlsx
+++ b/tests/fixtures/kb/past_answers/past_answer_2024.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>情報セキュリティポリシー v3.2に基づき運用中。年次レビューを2024年4月に完了。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>2024年度改定でクラウドセキュリティ条項を追加</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -478,22 +478,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>一部実施している</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>リスクアセスメント手順書(RA-PROC-2024)に従い、年2回の定期評価を実施。直近は2024年9月に完了。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>新規クラウドサービス導入時の追加アセスメントプロセスも整備済み</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>統合ID管理基盤(IAM-Core v2.1)により全システムのアクセス権を一元管理。四半期ごとの棚卸を実施。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>特権ID管理ツール(CyberArk PAM)を2024年6月に導入完了</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -532,22 +532,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>計画中</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>全重要システムにMFA導入済み（TOTP方式）。VPN接続時も必須化。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>レガシーシステム2件は2025年3月までに対応予定</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>次世代ファイアウォール(Palo Alto PA-5260)によるゾーン分離を実施。IPS/IDSも統合運用中。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>マイクロセグメンテーション対応を2024年度に完了</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>統合SIEM基盤(Splunk Enterprise)で全システムのログを集約・分析。リアルタイムアラート設定済み。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>ログ保存期間を5年から7年に延長（金融庁ガイドライン対応）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>一部実施している</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>CSIRT体制を構築済み。インシデント対応手順書(IRP-2024-v2)に基づき、年4回の訓練を実施。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>2024年8月にランサムウェア対応シナリオの机上演習を実施</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>脆弱性管理プラットフォーム(Tenable.io)により全資産の脆弱性を継続的にスキャン。CVSS 7.0以上は72時間以内に対応。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>ゼロデイ対応フローを2024年5月に改定</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>計画中</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>全データベースでAES-256暗号化を適用。鍵管理はHSM(Thales Luna)で一元管理。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>鍵ローテーション周期を年1回から半期1回に変更</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>全外部通信および社内重要通信にTLS 1.3を適用済み。TLS 1.0/1.1は全面廃止完了。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>2024年3月にTLS 1.0/1.1の完全廃止を達成</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>3-2-1ルールに基づくバックアップ体制を運用中。四半期ごとのリストアテスト実施。RTO=4時間、RPO=1時間。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>遠隔地バックアップサイトを東西2拠点体制に拡充（2024年7月）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -748,22 +748,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>一部実施している</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>BCP基本計画書(BCP-2024-Master)に基づき運用。DR訓練を年2回実施。直近は2024年10月に本番切替訓練を完了。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>クラウドDR環境（AWS東京/大阪リージョン）の整備完了</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>データセンターはISO 27001認証取得済み施設を利用。入退室はICカード＋生体認証の二要素で管理。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>監視カメラ映像のAI異常検知を2024年4月より運用開始</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -802,22 +802,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>計画中</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>委託先管理規程(OUT-MGT-2024)に基づき、年次セキュリティ監査を全委託先に実施。リスク評価に応じた管理区分を適用。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>再委託先の管理強化のため、サプライチェーンリスク評価を新規導入</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>全従業員向けeラーニング（年2回必須）および役職別専門研修を実施。受講率99.2%（2024年度上期）。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>標的型メール訓練を四半期ごとに実施、開封率は3.1%まで低下</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>EDR(CrowdStrike Falcon)を全端末に導入済み。サンドボックス型メールフィルタリング(FireEye EX)も併用。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>振る舞い検知ルールのチューニングを月次で実施</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>一部実施している</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>変更管理プロセス(CHG-PROC-v3)に基づき、CAB（変更諮問委員会）による承認制を運用。ServiceNowで一元管理。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>緊急変更の事後承認プロセスを改善（2024年度）</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>セキュアコーディングガイドライン(SCG-2024)を策定・適用。CI/CDパイプラインにSAST/DAST(Checkmarx, OWASP ZAP)を組込み。</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>コンテナセキュリティスキャン(Trivy)も2024年から追加</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -937,22 +937,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>計画中</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>クラウドセキュリティ管理基準(CSP-STD-2024)に基づき運用。CSPM(Prisma Cloud)で構成監視を自動化。</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>マルチクラウド環境（AWS/Azure）の統合セキュリティ監視を実現</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -969,15 +969,285 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>個人情報保護管理規程(PII-MGT-v4)およびプライバシーポリシーに基づき運用。DLP(Symantec DLP)で漏洩防止を実施。</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024年度対応</t>
+          <t>プライバシー影響評価(PIA)プロセスを全新規サービスに適用</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>特権ID管理ツール(CyberArk PAM)で全特権アカウントを管理。操作ログの録画・監査を実施。パスワード自動ローテーション適用。</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>共有アカウントの廃止を2024年9月に完了</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>API管理基盤(Kong Gateway)で全外部連携を一元管理。OAuth 2.0/OpenID Connectによる認証・認可を標準適用。</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>API利用状況のリアルタイム監視ダッシュボードを構築</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MDM(Microsoft Intune)で全業務用モバイル端末を管理。リモートワイプ機能を有効化。端末暗号化を必須化。</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BYODポリシーを改定し、MAM（モバイルアプリ管理）を適用</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>内部監査部門による年次IT監査を実施。2024年度監査報告書(IA-RPT-2024-012)で指摘事項なし。外部監査(SOC2 Type II)も取得。</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>監査証跡の自動収集ツールを導入し、工数を40%削減</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>コンプライアンス管理システム(GRC-Platform)で法令改正の追跡と対応状況を管理。金融庁ガイドライン改正への対応を随時実施。</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2024年改正個人情報保護法への対応完了（2024年6月）</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>メールセキュリティゲートウェイ(Proofpoint)を導入。DMARC/DKIM/SPF全対応。添付ファイルのサンドボックス検査を実施。</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DMARCポリシーをquarantineからrejectに変更（2024年8月）</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IT資産管理ツール(SKYSEA Client View)で全ハードウェア・ソフトウェアを台帳管理。月次棚卸と自動検出による差分チェックを実施。</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>シャドーIT検出機能を2024年度に強化</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>セキュリティKPIダッシュボード(Grafana)を運用。月次で経営層へ報告。主要指標：パッチ適用率98.5%、インシデント平均対応時間2.3時間。</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>KPI項目にサプライチェーンリスクスコアを追加（2024年度）</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ゼロトラストアーキテクチャ移行計画(ZTA-PLAN-2024)に基づき段階的に実施。SDP(Zscaler Private Access)を主要システムに導入済み。</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ネットワークアクセス制御の80%をゼロトラストモデルに移行完了</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>年2回のサイバー演習を実施。2024年度は金融ISAC主催の業界横断演習にも参加。TLPTを重要システム3件に対して実施完了。</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Red Team演習の結果を踏まえたブルーチーム強化策を実施中</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>高</t>
         </is>
